--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q10_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01027852009034689</v>
+        <v>0.009885839748077965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01027852009034689</v>
+        <v>0.009885839748077965</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01021588771523946</v>
+        <v>0.009815074296896559</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01021588771523946</v>
+        <v>0.009815074296896559</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01011583640292518</v>
+        <v>0.009704127454192626</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01011583640292518</v>
+        <v>0.009704127454192626</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.009990003193595106</v>
+        <v>0.009569716520828971</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009990003193595106</v>
+        <v>0.009569716520828971</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00986959935545609</v>
+        <v>0.00944068701410565</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00986959935545609</v>
+        <v>0.00944068701410565</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009783718411799956</v>
+        <v>0.009353456298901422</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009783718411799956</v>
+        <v>0.009353456298901422</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.009756719001615694</v>
+        <v>0.009330974289133594</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009756719001615694</v>
+        <v>0.009330974289133594</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.009817471402257368</v>
+        <v>0.009400262868001391</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009817471402257368</v>
+        <v>0.009400262868001391</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01001204204223739</v>
+        <v>0.009606596848600739</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01001204204223739</v>
+        <v>0.009606596848600739</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01033578331633768</v>
+        <v>0.009944734338051344</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01033578331633768</v>
+        <v>0.009944734338051344</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01082590585693647</v>
+        <v>0.01044996788511493</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01082590585693647</v>
+        <v>0.01044996788511493</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01150667532261644</v>
+        <v>0.01114558962988691</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01150667532261644</v>
+        <v>0.01114558962988691</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0123943469451725</v>
+        <v>0.01204637350832067</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0123943469451725</v>
+        <v>0.01204637350832067</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01349358402042588</v>
+        <v>0.01315571182027099</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01349358402042588</v>
+        <v>0.01315571182027099</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01479596125184351</v>
+        <v>0.01446909925243227</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01479596125184351</v>
+        <v>0.01446909925243227</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01628140763116287</v>
+        <v>0.0159500486922919</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01628140763116287</v>
+        <v>0.0159500486922919</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01790268453270865</v>
+        <v>0.01756403505776701</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01790268453270865</v>
+        <v>0.01756403505776701</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01962583130777457</v>
+        <v>0.01927024857906189</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01962583130777457</v>
+        <v>0.01927024857906189</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02143543349497706</v>
+        <v>0.02105188930924103</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02143543349497706</v>
+        <v>0.02105188930924103</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02328123997081977</v>
+        <v>0.02285577006570626</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02328123997081977</v>
+        <v>0.02285577006570626</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02514285442926797</v>
+        <v>0.024664205148052</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02514285442926797</v>
+        <v>0.024664205148052</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02700298431223635</v>
+        <v>0.02646070427966285</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02700298431223635</v>
+        <v>0.02646070427966285</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02883389572418365</v>
+        <v>0.0282206891773246</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02883389572418365</v>
+        <v>0.0282206891773246</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03070048766461124</v>
+        <v>0.03001206960220565</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03070048766461124</v>
+        <v>0.03001206960220565</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03270389475222333</v>
+        <v>0.03193895488316904</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03270389475222333</v>
+        <v>0.03193895488316904</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.03484786916881403</v>
+        <v>0.03400860546552836</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03484786916881403</v>
+        <v>0.03400860546552836</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.03712743734506091</v>
+        <v>0.03621859235140883</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03712743734506091</v>
+        <v>0.03621859235140883</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.03953017014307213</v>
+        <v>0.03855804595130499</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03953017014307213</v>
+        <v>0.03855804595130499</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.04211954532328214</v>
+        <v>0.04108873449691566</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04211954532328214</v>
+        <v>0.04108873449691566</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.04470808910429683</v>
+        <v>0.04362847506796119</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04470808910429683</v>
+        <v>0.04362847506796119</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
